--- a/ППД_Н.xlsx
+++ b/ППД_Н.xlsx
@@ -45,7 +45,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -390,13 +391,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A14:J54"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A14:J47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="25.85546875" customWidth="1" min="3" max="3"/>
-    <col width="26.85546875" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="21.28515625" customWidth="1" min="10" max="10"/>
+    <col width="25.85546875" customWidth="1" style="1" min="3" max="3"/>
+    <col width="26.85546875" customWidth="1" style="1" min="5" max="5"/>
+    <col width="15" customWidth="1" style="1" min="6" max="6"/>
+    <col width="21.5703125" customWidth="1" style="1" min="7" max="7"/>
+    <col width="19.5703125" customWidth="1" style="1" min="8" max="8"/>
+    <col width="21.28515625" customWidth="1" style="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="14">
@@ -585,114 +588,67 @@
         <v>61000533266</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>1</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>КНС-3 Холмогорское м/р_ХМАО</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>ЦНС 180-1422-2ИТ</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>НА-8</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>17</v>
-      </c>
-      <c r="J26" t="n">
-        <v>61000329246</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>КНС-1А Спорышевское м/р</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>ЦНС 240-1660-2ТМ</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>НА-6</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>7</v>
-      </c>
-      <c r="J27" t="n">
-        <v>61000313869</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>1</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>КНС-1А Спорышевское м/р</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>ЦНС 240-1650-2ИТ</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>НА-7</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>26</v>
-      </c>
-      <c r="J28" t="n">
-        <v>61000235346</v>
-      </c>
-    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>№ п/п</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ЦЕХ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Работы по текущему ремонту!!!</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Дата выполнения работ</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Подпись, ФИО механика (мастера)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>№ ЗАКАЗА САП ТОРО</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Объект</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Оборудование</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Марка оборудования</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Рег. №</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Зав №</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="29">
       <c r="A29" t="n">
         <v>1</v>
@@ -704,7 +660,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>КНС-1Б Спорышевское м/р</t>
+          <t>КНС-3 Холмогорское м/р_ХМАО</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -714,19 +670,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ЦНС 240-1650-2ТМ</t>
+          <t>ЦНС 180-1422-2ИТ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>НА-10</t>
+          <t>НА-8</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>61000235329</v>
+        <v>61000329246</v>
       </c>
     </row>
     <row r="30">
@@ -740,7 +696,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>КНС-1В Спорышевское м/р</t>
+          <t>КНС-1А Спорышевское м/р</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -750,21 +706,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ЦНС 240-1050-2ИТ</t>
+          <t>ЦНС 240-1660-2ТМ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>НА-13</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+          <t>НА-6</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>7</v>
       </c>
       <c r="J30" t="n">
-        <v>61000153881</v>
+        <v>61000313869</v>
       </c>
     </row>
     <row r="31">
@@ -778,7 +732,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>КНС-3 Спорышевское м/р</t>
+          <t>КНС-1А Спорышевское м/р</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -788,19 +742,19 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>НЦС К 310-1510-УХЛ4</t>
+          <t>ЦНС 240-1650-2ИТ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>НА-2</t>
+          <t>НА-7</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2070</v>
+        <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>61000113163</v>
+        <v>61000235346</v>
       </c>
     </row>
     <row r="32">
@@ -814,129 +768,292 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>КНС-1Б Спорышевское м/р</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ЦНС 240-1650-2ТМ</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>НА-10</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>86</v>
+      </c>
+      <c r="J32" t="n">
+        <v>61000235329</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ЦППД-1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>КНС-1В Спорышевское м/р</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ЦНС 240-1050-2ИТ</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>НА-13</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>61000153881</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ЦППД-1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>КНС-3 Спорышевское м/р</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>НЦС К 310-1510-УХЛ4</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>НА-2</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>2070</v>
+      </c>
+      <c r="J34" t="n">
+        <v>61000113163</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ЦППД-1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>КНС-3 Спорышевское м/р</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>ЦНС 310-1510-2И1Т</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>НА-4</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>240-28</t>
         </is>
       </c>
-      <c r="J32" t="n">
+      <c r="J35" t="n">
         <v>61000313869</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>1</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>КНС-3 Холмогорское м/р_ХМАО</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>№ п/п</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ЦЕХ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Работы по замене агрегатов</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Дата выполнения работ</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Подпись, ФИО механика (мастера)</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>№ ЗАКАЗА САП ТОРО</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Объект</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Рег. №</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Демонтаж</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Монтаж/ПНР</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Марка оборудования</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ЦППД-1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>КНС-1Б Спорышевское м/р</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>НА-9</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ЦНС 180-1422-2ТМ </t>
-        </is>
-      </c>
-      <c r="J52" t="n">
-        <v>61000541514</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>1</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>КНС-1Б Спорышевское м/р</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>НА-9</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>885</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>НЦНС-К-310-1510-УХЛ4</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
-        <v>61000173330</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>1</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ЦНС 240-1660-2ТМ</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>61000383673</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ЦППД-1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
         <is>
           <t>КНС-3 Спорышевское м/р</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>НА-1</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v>2</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>ЦНС 240-1660-2ТМ</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>61000294385</v>
+      <c r="E47" t="n">
+        <v>59</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ЦНС 240-1650-2ТМ</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>61000312020</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="H41:H44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="C41:G42"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="I41:I44"/>
+    <mergeCell ref="I22:I25"/>
+    <mergeCell ref="A41:A44"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="H22:H25"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="J22:J25"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="J41:J44"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="B41:B44"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="C22:G23"/>
+    <mergeCell ref="F24:F25"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/ППД_Н.xlsx
+++ b/ППД_Н.xlsx
@@ -16,13 +16,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000000FF"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="2">
@@ -45,9 +50,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -916,7 +922,7 @@
           <t>ЦЕХ</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Работы по замене агрегатов</t>
         </is>
@@ -1031,8 +1037,8 @@
   </sheetData>
   <mergeCells count="22">
     <mergeCell ref="B22:B25"/>
+    <mergeCell ref="E43:E44"/>
     <mergeCell ref="H41:H44"/>
-    <mergeCell ref="E43:E44"/>
     <mergeCell ref="C41:G42"/>
     <mergeCell ref="G43:G44"/>
     <mergeCell ref="I41:I44"/>

--- a/ППД_Н.xlsx
+++ b/ППД_Н.xlsx
@@ -6,7 +6,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справка" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -16,13 +16,28 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0000FF"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
@@ -50,15 +65,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -141,44 +166,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -205,15 +230,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -240,7 +264,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -252,142 +275,166 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -397,17 +444,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A14:J47"/>
+  <dimension ref="A2:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="25.85546875" customWidth="1" style="1" min="3" max="3"/>
-    <col width="26.85546875" customWidth="1" style="1" min="5" max="5"/>
-    <col width="15" customWidth="1" style="1" min="6" max="6"/>
-    <col width="21.5703125" customWidth="1" style="1" min="7" max="7"/>
+    <col width="6.28515625" customWidth="1" style="1" min="1" max="1"/>
+    <col width="29.28515625" customWidth="1" style="1" min="3" max="3"/>
+    <col width="13.28515625" customWidth="1" style="1" min="4" max="4"/>
+    <col width="20.28515625" customWidth="1" style="1" min="5" max="5"/>
+    <col width="25.28515625" customWidth="1" style="1" min="6" max="6"/>
+    <col width="17.7109375" customWidth="1" style="1" min="7" max="7"/>
     <col width="19.5703125" customWidth="1" style="1" min="8" max="8"/>
-    <col width="21.28515625" customWidth="1" style="1" min="10" max="10"/>
+    <col width="15.28515625" customWidth="1" style="1" min="9" max="9"/>
+    <col width="17" customWidth="1" style="1" min="10" max="10"/>
   </cols>
   <sheetData>
+    <row r="2">
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>ООО "ЯмалСпецЦентр"</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>(Наименование организации)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>СПРАВКА №04</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> о выполнении сервисных работ за</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>сентябрь</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2026 года</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> на объектах ЦППН-1 Акционерного Общества "Газпромнефть-Ноябрьскнефтегаз"(Ноябрьский регион)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>№ п/п</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ЦЕХ</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Работы по  сервисному обслуживанию</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Дата выполнения работ</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Подпись, ФИО механика (мастера)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>№ ЗАКАЗА САП ТОРО</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Объект</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Оборудование</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Марка оборудования</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Рег. №</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Зав №</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="14">
       <c r="A14" t="n">
         <v>1</v>
@@ -434,7 +590,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>НА-5</t>
+          <t>НА-5 СО</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -467,19 +623,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>НЦС 240-1650-15061-УХЛ4</t>
+          <t>ЦНС 240-1660-2ТМ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>НА-8</t>
+          <t>НА-6 СО</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2422</v>
+        <v>7</v>
       </c>
       <c r="J15" t="n">
-        <v>61000491174</v>
+        <v>61000111457</v>
       </c>
     </row>
     <row r="16">
@@ -503,21 +659,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ЦНС 240-1660-2ТМ</t>
+          <t>ЦНС 240-1650-2ИТ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>НА-14</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>002-3</t>
-        </is>
+          <t>НА-7 СО</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>61000310495</v>
+        <v>61000235346</v>
       </c>
     </row>
     <row r="17">
@@ -531,7 +685,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>КНС-1В Спорышевское м/р</t>
+          <t>КНС-1А Спорышевское м/р</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -541,21 +695,21 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ЦНС 240-1050-2ТМ</t>
+          <t>ЦНС 240-1660-2ТМ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>НА-11</t>
+          <t>НА-14 СО</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20086/002-1</t>
+          <t>002-3</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>61000313869</v>
+        <v>61000310495</v>
       </c>
     </row>
     <row r="18">
@@ -569,274 +723,350 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>КНС-1Б Спорышевское м/р</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>НЦНС-К-310-1510-УХЛ4</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>НА-9 СО</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>885</v>
+      </c>
+      <c r="J18" t="n">
+        <v>61000173330</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ЦППД-1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>КНС-1Б Спорышевское м/р</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ЦНС 240-1650-2ТМ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>НА-10 СО</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>86</v>
+      </c>
+      <c r="J19" t="n">
+        <v>61000235329</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ЦППД-1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>КНС-1В Спорышевское м/р</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ЦНС 240-1050-2ТМ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>НА-11 СО</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>20086/002-1</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>61000312019</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ЦППД-1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>КНС-1В Спорышевское м/р</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ЦНС 240-1050-2ИТ</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>НА-13 СО</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>61000153881</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ЦППД-1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>КНС-3 Спорышевское м/р</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ЦНС 240-1660-2ТМ</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>НА-1 СО</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>61000294385</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ЦППД-1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>КНС-3 Спорышевское м/р</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>НЦС К 310-1510-УХЛ4</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>НА-2 СО</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>2070</v>
+      </c>
+      <c r="J23" t="n">
+        <v>61000113163</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ЦППД-1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>КНС-3 Спорышевское м/р</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>ЦНСс 310-1510-ПП-К-Т1-УХЛ4</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>НА-3</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>НА-3 СО</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
         <v>25074002096</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J24" t="n">
         <v>61000533266</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ЦППД-1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>КНС-3 Спорышевское м/р</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ЦНС 310-1510-2И1Т</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>НА-4 СО</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>240-28</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>61000313869</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>ЦЕХ</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Работы по текущему ремонту!!!</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Работы по текущему ремонту</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>Дата выполнения работ</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>Подпись, ФИО механика (мастера)</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>№ ЗАКАЗА САП ТОРО</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="C24" t="inlineStr">
+    <row r="31"/>
+    <row r="32">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Оборудование</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Марка оборудования</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Рег. №</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Зав №</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>1</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>КНС-3 Холмогорское м/р_ХМАО</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>ЦНС 180-1422-2ИТ</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>НА-8</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>17</v>
-      </c>
-      <c r="J29" t="n">
-        <v>61000329246</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>1</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>КНС-1А Спорышевское м/р</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>ЦНС 240-1660-2ТМ</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>НА-6</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>7</v>
-      </c>
-      <c r="J30" t="n">
-        <v>61000313869</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>1</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>КНС-1А Спорышевское м/р</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>ЦНС 240-1650-2ИТ</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>НА-7</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>26</v>
-      </c>
-      <c r="J31" t="n">
-        <v>61000235346</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>1</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>КНС-1Б Спорышевское м/р</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>ЦНС 240-1650-2ТМ</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>НА-10</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>86</v>
-      </c>
-      <c r="J32" t="n">
-        <v>61000235329</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>1</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>КНС-1В Спорышевское м/р</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>насос</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>ЦНС 240-1050-2ИТ</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>НА-13</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>61000153881</v>
-      </c>
-    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="n">
         <v>1</v>
@@ -848,7 +1078,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>КНС-3 Спорышевское м/р</t>
+          <t>КНС-1 Карамовское м/р</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -858,19 +1088,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>НЦС К 310-1510-УХЛ4</t>
+          <t>ЦНСс-310-1510-ПП-К-Т1-УХЛ4</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>НА-2</t>
+          <t>НА-1 ТР</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2070</v>
+        <v>25074002097</v>
       </c>
       <c r="J34" t="n">
-        <v>61000113163</v>
+        <v>61000533265</v>
       </c>
     </row>
     <row r="35">
@@ -884,7 +1114,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>КНС-3 Спорышевское м/р</t>
+          <t>КНС-3 Холмогорское м/р_ХМАО</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -894,172 +1124,197 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ЦНС 310-1510-2И1Т</t>
+          <t>ЦНС 240-1422-2ТМ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>НА-4</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>240-28</t>
-        </is>
+          <t>НА-7 ТР</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>10</v>
       </c>
       <c r="J35" t="n">
-        <v>61000313869</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+        <v>61000173560</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ЦППД-1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>КНС-1А Спорышевское м/р</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>НЦС 240-1650-15061-УХЛ4</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>НА-8 ТР</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>2422</v>
+      </c>
+      <c r="J36" t="n">
+        <v>61000491174</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ЦППД-1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>КНС Средне-Итурское м/р</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>насос</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ЦНС 180-1422Мт</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>НА-5 ТР</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>338</v>
+      </c>
+      <c r="J37" t="n">
+        <v>61000387520</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1" s="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>ЦЕХ</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>Работы по замене агрегатов</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Дата выполнения работ</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>Подпись, ФИО механика (мастера)</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>№ ЗАКАЗА САП ТОРО</t>
         </is>
       </c>
     </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="C43" t="inlineStr">
+    <row r="48"/>
+    <row r="49">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Рег. №</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Демонтаж</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Монтаж/ПНР</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Марка оборудования</t>
         </is>
       </c>
     </row>
-    <row r="44"/>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>1</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>КНС-1Б Спорышевское м/р</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>НА-9</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>ЦНС 240-1660-2ТМ</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>61000383673</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>1</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>ЦППД-1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>КНС-3 Спорышевское м/р</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>НА-1</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>59</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>ЦНС 240-1650-2ТМ</t>
-        </is>
-      </c>
-      <c r="J47" t="n">
-        <v>61000312020</v>
-      </c>
-    </row>
+    <row r="50"/>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="H41:H44"/>
-    <mergeCell ref="C41:G42"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="I41:I44"/>
-    <mergeCell ref="I22:I25"/>
-    <mergeCell ref="A41:A44"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="H22:H25"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="J22:J25"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="J41:J44"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B41:B44"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="C22:G23"/>
-    <mergeCell ref="F24:F25"/>
+  <mergeCells count="40">
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="I30:I33"/>
+    <mergeCell ref="B47:B50"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="H9:H12"/>
+    <mergeCell ref="J9:J12"/>
+    <mergeCell ref="H5"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="F4"/>
+    <mergeCell ref="I47:I50"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="J30:J33"/>
+    <mergeCell ref="C47:G48"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="C9:G10"/>
+    <mergeCell ref="F3"/>
+    <mergeCell ref="H47:H50"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="C30:G31"/>
+    <mergeCell ref="J47:J50"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A47:A50"/>
+    <mergeCell ref="F2"/>
+    <mergeCell ref="I9:I12"/>
+    <mergeCell ref="D6:I6"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H30:H33"/>
+    <mergeCell ref="G5"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ППД_Н.xlsx
+++ b/ППД_Н.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,10 @@
       <color rgb="000000FF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -65,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -77,6 +81,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -473,7 +480,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>СПРАВКА №04</t>
         </is>
@@ -485,9 +492,9 @@
           <t xml:space="preserve"> о выполнении сервисных работ за</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>сентябрь</t>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>октябрь</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -604,7 +611,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -640,7 +647,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -676,7 +683,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -714,7 +721,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -750,7 +757,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -786,7 +793,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -824,7 +831,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -862,7 +869,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -898,7 +905,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -934,7 +941,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -970,7 +977,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1105,7 +1112,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1141,7 +1148,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1177,7 +1184,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
